--- a/tests/TC-19/results/timetable_all_departments_even.xlsx
+++ b/tests/TC-19/results/timetable_all_departments_even.xlsx
@@ -80,8 +80,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFDAB3"/>
-        <bgColor rgb="00FFDAB3"/>
+        <fgColor rgb="00C8E6C9"/>
+        <bgColor rgb="00C8E6C9"/>
       </patternFill>
     </fill>
     <fill>
@@ -92,8 +92,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C8E6C9"/>
-        <bgColor rgb="00C8E6C9"/>
+        <fgColor rgb="00FFDAB3"/>
+        <bgColor rgb="00FFDAB3"/>
       </patternFill>
     </fill>
     <fill>
@@ -203,10 +203,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
     </xf>
   </cellXfs>
@@ -844,19 +844,19 @@
         </is>
       </c>
       <c r="C2" s="8" t="inlineStr"/>
-      <c r="D2" s="9" t="inlineStr">
-        <is>
-          <t>CS201
+      <c r="D2" s="8" t="inlineStr"/>
+      <c r="E2" s="8" t="inlineStr"/>
+      <c r="F2" s="9" t="inlineStr">
+        <is>
+          <t>CS202
 LEC
 Room: 101
-Dr. A</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="n"/>
-      <c r="F2" s="10" t="n"/>
-      <c r="G2" s="11" t="n"/>
-      <c r="H2" s="8" t="inlineStr"/>
-      <c r="I2" s="8" t="inlineStr"/>
+Dr. B</t>
+        </is>
+      </c>
+      <c r="G2" s="10" t="n"/>
+      <c r="H2" s="10" t="n"/>
+      <c r="I2" s="11" t="n"/>
       <c r="J2" s="8" t="inlineStr"/>
       <c r="K2" s="8" t="inlineStr"/>
       <c r="L2" s="12" t="inlineStr">
@@ -871,7 +871,14 @@
       <c r="Q2" s="8" t="inlineStr"/>
       <c r="R2" s="8" t="inlineStr"/>
       <c r="S2" s="8" t="inlineStr"/>
-      <c r="T2" s="8" t="inlineStr"/>
+      <c r="T2" s="13" t="inlineStr">
+        <is>
+          <t>CS201
+TUT
+Room: 101
+Dr. A</t>
+        </is>
+      </c>
       <c r="U2" s="7" t="inlineStr">
         <is>
           <t>Minor Slot</t>
@@ -889,7 +896,8 @@
           <t>Minor Slot</t>
         </is>
       </c>
-      <c r="C3" s="9" t="inlineStr">
+      <c r="C3" s="8" t="inlineStr"/>
+      <c r="D3" s="13" t="inlineStr">
         <is>
           <t>CS201
 LEC
@@ -897,10 +905,9 @@
 Dr. A</t>
         </is>
       </c>
-      <c r="D3" s="11" t="n"/>
-      <c r="E3" s="8" t="inlineStr"/>
-      <c r="F3" s="8" t="inlineStr"/>
-      <c r="G3" s="8" t="inlineStr"/>
+      <c r="E3" s="10" t="n"/>
+      <c r="F3" s="10" t="n"/>
+      <c r="G3" s="11" t="n"/>
       <c r="H3" s="8" t="inlineStr"/>
       <c r="I3" s="8" t="inlineStr"/>
       <c r="J3" s="8" t="inlineStr"/>
@@ -913,8 +920,7 @@
       <c r="M3" s="8" t="inlineStr"/>
       <c r="N3" s="8" t="inlineStr"/>
       <c r="O3" s="8" t="inlineStr"/>
-      <c r="P3" s="8" t="inlineStr"/>
-      <c r="Q3" s="13" t="inlineStr">
+      <c r="P3" s="9" t="inlineStr">
         <is>
           <t>CS202
 LEC
@@ -922,8 +928,9 @@
 Dr. B</t>
         </is>
       </c>
-      <c r="R3" s="10" t="n"/>
-      <c r="S3" s="11" t="n"/>
+      <c r="Q3" s="10" t="n"/>
+      <c r="R3" s="11" t="n"/>
+      <c r="S3" s="8" t="inlineStr"/>
       <c r="T3" s="8" t="inlineStr"/>
       <c r="U3" s="7" t="inlineStr">
         <is>
@@ -946,32 +953,25 @@
       <c r="D4" s="8" t="inlineStr"/>
       <c r="E4" s="8" t="inlineStr"/>
       <c r="F4" s="8" t="inlineStr"/>
-      <c r="G4" s="13" t="inlineStr">
-        <is>
-          <t>CS202
+      <c r="G4" s="8" t="inlineStr"/>
+      <c r="H4" s="8" t="inlineStr"/>
+      <c r="I4" s="8" t="inlineStr"/>
+      <c r="J4" s="8" t="inlineStr"/>
+      <c r="K4" s="8" t="inlineStr"/>
+      <c r="L4" s="12" t="inlineStr">
+        <is>
+          <t>LUNCH BREAK</t>
+        </is>
+      </c>
+      <c r="M4" s="13" t="inlineStr">
+        <is>
+          <t>CS201
 LEC
 Room: 101
-Dr. B</t>
-        </is>
-      </c>
-      <c r="H4" s="10" t="n"/>
-      <c r="I4" s="10" t="n"/>
-      <c r="J4" s="11" t="n"/>
-      <c r="K4" s="8" t="inlineStr"/>
-      <c r="L4" s="12" t="inlineStr">
-        <is>
-          <t>LUNCH BREAK</t>
-        </is>
-      </c>
-      <c r="M4" s="8" t="inlineStr"/>
-      <c r="N4" s="9" t="inlineStr">
-        <is>
-          <t>CS201
-TUT
-Room: 101
 Dr. A</t>
         </is>
       </c>
+      <c r="N4" s="11" t="n"/>
       <c r="O4" s="8" t="inlineStr"/>
       <c r="P4" s="8" t="inlineStr"/>
       <c r="Q4" s="8" t="inlineStr"/>
@@ -1159,10 +1159,10 @@
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="D2:G2"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="G4:J4"/>
-    <mergeCell ref="Q3:S3"/>
+    <mergeCell ref="M4:N4"/>
+    <mergeCell ref="P3:R3"/>
+    <mergeCell ref="F2:I2"/>
+    <mergeCell ref="D3:G3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1320,19 +1320,19 @@
         </is>
       </c>
       <c r="C2" s="8" t="inlineStr"/>
-      <c r="D2" s="9" t="inlineStr">
-        <is>
-          <t>CS201
+      <c r="D2" s="8" t="inlineStr"/>
+      <c r="E2" s="8" t="inlineStr"/>
+      <c r="F2" s="9" t="inlineStr">
+        <is>
+          <t>CS202
 LEC
 Room: 101
-Dr. A</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="n"/>
-      <c r="F2" s="10" t="n"/>
-      <c r="G2" s="11" t="n"/>
-      <c r="H2" s="8" t="inlineStr"/>
-      <c r="I2" s="8" t="inlineStr"/>
+Dr. B</t>
+        </is>
+      </c>
+      <c r="G2" s="10" t="n"/>
+      <c r="H2" s="10" t="n"/>
+      <c r="I2" s="11" t="n"/>
       <c r="J2" s="8" t="inlineStr"/>
       <c r="K2" s="8" t="inlineStr"/>
       <c r="L2" s="12" t="inlineStr">
@@ -1347,7 +1347,14 @@
       <c r="Q2" s="8" t="inlineStr"/>
       <c r="R2" s="8" t="inlineStr"/>
       <c r="S2" s="8" t="inlineStr"/>
-      <c r="T2" s="8" t="inlineStr"/>
+      <c r="T2" s="13" t="inlineStr">
+        <is>
+          <t>CS201
+TUT
+Room: 101
+Dr. A</t>
+        </is>
+      </c>
       <c r="U2" s="7" t="inlineStr">
         <is>
           <t>Minor Slot</t>
@@ -1365,7 +1372,8 @@
           <t>Minor Slot</t>
         </is>
       </c>
-      <c r="C3" s="9" t="inlineStr">
+      <c r="C3" s="8" t="inlineStr"/>
+      <c r="D3" s="13" t="inlineStr">
         <is>
           <t>CS201
 LEC
@@ -1373,10 +1381,9 @@
 Dr. A</t>
         </is>
       </c>
-      <c r="D3" s="11" t="n"/>
-      <c r="E3" s="8" t="inlineStr"/>
-      <c r="F3" s="8" t="inlineStr"/>
-      <c r="G3" s="8" t="inlineStr"/>
+      <c r="E3" s="10" t="n"/>
+      <c r="F3" s="10" t="n"/>
+      <c r="G3" s="11" t="n"/>
       <c r="H3" s="8" t="inlineStr"/>
       <c r="I3" s="8" t="inlineStr"/>
       <c r="J3" s="8" t="inlineStr"/>
@@ -1389,8 +1396,7 @@
       <c r="M3" s="8" t="inlineStr"/>
       <c r="N3" s="8" t="inlineStr"/>
       <c r="O3" s="8" t="inlineStr"/>
-      <c r="P3" s="8" t="inlineStr"/>
-      <c r="Q3" s="13" t="inlineStr">
+      <c r="P3" s="9" t="inlineStr">
         <is>
           <t>CS202
 LEC
@@ -1398,8 +1404,9 @@
 Dr. B</t>
         </is>
       </c>
-      <c r="R3" s="10" t="n"/>
-      <c r="S3" s="11" t="n"/>
+      <c r="Q3" s="10" t="n"/>
+      <c r="R3" s="11" t="n"/>
+      <c r="S3" s="8" t="inlineStr"/>
       <c r="T3" s="8" t="inlineStr"/>
       <c r="U3" s="7" t="inlineStr">
         <is>
@@ -1422,32 +1429,25 @@
       <c r="D4" s="8" t="inlineStr"/>
       <c r="E4" s="8" t="inlineStr"/>
       <c r="F4" s="8" t="inlineStr"/>
-      <c r="G4" s="13" t="inlineStr">
-        <is>
-          <t>CS202
+      <c r="G4" s="8" t="inlineStr"/>
+      <c r="H4" s="8" t="inlineStr"/>
+      <c r="I4" s="8" t="inlineStr"/>
+      <c r="J4" s="8" t="inlineStr"/>
+      <c r="K4" s="8" t="inlineStr"/>
+      <c r="L4" s="12" t="inlineStr">
+        <is>
+          <t>LUNCH BREAK</t>
+        </is>
+      </c>
+      <c r="M4" s="13" t="inlineStr">
+        <is>
+          <t>CS201
 LEC
 Room: 101
-Dr. B</t>
-        </is>
-      </c>
-      <c r="H4" s="10" t="n"/>
-      <c r="I4" s="10" t="n"/>
-      <c r="J4" s="11" t="n"/>
-      <c r="K4" s="8" t="inlineStr"/>
-      <c r="L4" s="12" t="inlineStr">
-        <is>
-          <t>LUNCH BREAK</t>
-        </is>
-      </c>
-      <c r="M4" s="8" t="inlineStr"/>
-      <c r="N4" s="9" t="inlineStr">
-        <is>
-          <t>CS201
-TUT
-Room: 101
 Dr. A</t>
         </is>
       </c>
+      <c r="N4" s="11" t="n"/>
       <c r="O4" s="8" t="inlineStr"/>
       <c r="P4" s="8" t="inlineStr"/>
       <c r="Q4" s="8" t="inlineStr"/>
@@ -1635,10 +1635,10 @@
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="D2:G2"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="G4:J4"/>
-    <mergeCell ref="Q3:S3"/>
+    <mergeCell ref="M4:N4"/>
+    <mergeCell ref="P3:R3"/>
+    <mergeCell ref="F2:I2"/>
+    <mergeCell ref="D3:G3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1795,8 +1795,15 @@
           <t>Minor Slot</t>
         </is>
       </c>
-      <c r="C2" s="8" t="inlineStr"/>
-      <c r="D2" s="8" t="inlineStr"/>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>CS402
+LEC
+Room: 101
+Dr. D</t>
+        </is>
+      </c>
+      <c r="D2" s="11" t="n"/>
       <c r="E2" s="8" t="inlineStr"/>
       <c r="F2" s="8" t="inlineStr"/>
       <c r="G2" s="8" t="inlineStr"/>
@@ -1809,26 +1816,19 @@
           <t>LUNCH BREAK</t>
         </is>
       </c>
-      <c r="M2" s="13" t="inlineStr">
-        <is>
-          <t>CS402
-LEC
-Room: 101
-Dr. D</t>
-        </is>
-      </c>
-      <c r="N2" s="11" t="n"/>
-      <c r="O2" s="8" t="inlineStr"/>
-      <c r="P2" s="9" t="inlineStr">
+      <c r="M2" s="8" t="inlineStr"/>
+      <c r="N2" s="8" t="inlineStr"/>
+      <c r="O2" s="13" t="inlineStr">
         <is>
           <t>CS401
-LEC
+TUT
 Room: 101
 Dr. C</t>
         </is>
       </c>
-      <c r="Q2" s="10" t="n"/>
-      <c r="R2" s="11" t="n"/>
+      <c r="P2" s="10" t="n"/>
+      <c r="Q2" s="11" t="n"/>
+      <c r="R2" s="8" t="inlineStr"/>
       <c r="S2" s="8" t="inlineStr"/>
       <c r="T2" s="8" t="inlineStr"/>
       <c r="U2" s="7" t="inlineStr">
@@ -1864,10 +1864,10 @@
       </c>
       <c r="M3" s="9" t="inlineStr">
         <is>
-          <t>CS401
+          <t>CS402
 LEC
 Room: 101
-Dr. C</t>
+Dr. D</t>
         </is>
       </c>
       <c r="N3" s="11" t="n"/>
@@ -1896,10 +1896,17 @@
       </c>
       <c r="C4" s="8" t="inlineStr"/>
       <c r="D4" s="8" t="inlineStr"/>
-      <c r="E4" s="8" t="inlineStr"/>
-      <c r="F4" s="8" t="inlineStr"/>
-      <c r="G4" s="8" t="inlineStr"/>
-      <c r="H4" s="8" t="inlineStr"/>
+      <c r="E4" s="13" t="inlineStr">
+        <is>
+          <t>CS401
+LEC
+Room: 101
+Dr. C</t>
+        </is>
+      </c>
+      <c r="F4" s="10" t="n"/>
+      <c r="G4" s="10" t="n"/>
+      <c r="H4" s="11" t="n"/>
       <c r="I4" s="8" t="inlineStr"/>
       <c r="J4" s="8" t="inlineStr"/>
       <c r="K4" s="8" t="inlineStr"/>
@@ -1937,10 +1944,17 @@
       <c r="D5" s="8" t="inlineStr"/>
       <c r="E5" s="8" t="inlineStr"/>
       <c r="F5" s="8" t="inlineStr"/>
-      <c r="G5" s="8" t="inlineStr"/>
-      <c r="H5" s="8" t="inlineStr"/>
-      <c r="I5" s="8" t="inlineStr"/>
-      <c r="J5" s="8" t="inlineStr"/>
+      <c r="G5" s="13" t="inlineStr">
+        <is>
+          <t>CS401
+LEC
+Room: 101
+Dr. C</t>
+        </is>
+      </c>
+      <c r="H5" s="10" t="n"/>
+      <c r="I5" s="10" t="n"/>
+      <c r="J5" s="11" t="n"/>
       <c r="K5" s="8" t="inlineStr"/>
       <c r="L5" s="12" t="inlineStr">
         <is>
@@ -1972,14 +1986,7 @@
           <t>Minor Slot</t>
         </is>
       </c>
-      <c r="C6" s="9" t="inlineStr">
-        <is>
-          <t>CS401
-TUT
-Room: 101
-Dr. C</t>
-        </is>
-      </c>
+      <c r="C6" s="8" t="inlineStr"/>
       <c r="D6" s="8" t="inlineStr"/>
       <c r="E6" s="8" t="inlineStr"/>
       <c r="F6" s="8" t="inlineStr"/>
@@ -1993,15 +2000,8 @@
           <t>LUNCH BREAK</t>
         </is>
       </c>
-      <c r="M6" s="13" t="inlineStr">
-        <is>
-          <t>CS402
-LEC
-Room: 101
-Dr. D</t>
-        </is>
-      </c>
-      <c r="N6" s="11" t="n"/>
+      <c r="M6" s="8" t="inlineStr"/>
+      <c r="N6" s="8" t="inlineStr"/>
       <c r="O6" s="8" t="inlineStr"/>
       <c r="P6" s="8" t="inlineStr"/>
       <c r="Q6" s="8" t="inlineStr"/>
@@ -2110,11 +2110,12 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="M6:N6"/>
-    <mergeCell ref="P2:R2"/>
-    <mergeCell ref="M2:N2"/>
+  <mergeCells count="5">
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="E4:H4"/>
+    <mergeCell ref="O2:Q2"/>
     <mergeCell ref="M3:N3"/>
+    <mergeCell ref="G5:J5"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2271,8 +2272,15 @@
           <t>Minor Slot</t>
         </is>
       </c>
-      <c r="C2" s="8" t="inlineStr"/>
-      <c r="D2" s="8" t="inlineStr"/>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>CS402
+LEC
+Room: 101
+Dr. D</t>
+        </is>
+      </c>
+      <c r="D2" s="11" t="n"/>
       <c r="E2" s="8" t="inlineStr"/>
       <c r="F2" s="8" t="inlineStr"/>
       <c r="G2" s="8" t="inlineStr"/>
@@ -2285,26 +2293,19 @@
           <t>LUNCH BREAK</t>
         </is>
       </c>
-      <c r="M2" s="13" t="inlineStr">
-        <is>
-          <t>CS402
-LEC
-Room: 101
-Dr. D</t>
-        </is>
-      </c>
-      <c r="N2" s="11" t="n"/>
-      <c r="O2" s="8" t="inlineStr"/>
-      <c r="P2" s="9" t="inlineStr">
+      <c r="M2" s="8" t="inlineStr"/>
+      <c r="N2" s="8" t="inlineStr"/>
+      <c r="O2" s="13" t="inlineStr">
         <is>
           <t>CS401
-LEC
+TUT
 Room: 101
 Dr. C</t>
         </is>
       </c>
-      <c r="Q2" s="10" t="n"/>
-      <c r="R2" s="11" t="n"/>
+      <c r="P2" s="10" t="n"/>
+      <c r="Q2" s="11" t="n"/>
+      <c r="R2" s="8" t="inlineStr"/>
       <c r="S2" s="8" t="inlineStr"/>
       <c r="T2" s="8" t="inlineStr"/>
       <c r="U2" s="7" t="inlineStr">
@@ -2340,10 +2341,10 @@
       </c>
       <c r="M3" s="9" t="inlineStr">
         <is>
-          <t>CS401
+          <t>CS402
 LEC
 Room: 101
-Dr. C</t>
+Dr. D</t>
         </is>
       </c>
       <c r="N3" s="11" t="n"/>
@@ -2372,10 +2373,17 @@
       </c>
       <c r="C4" s="8" t="inlineStr"/>
       <c r="D4" s="8" t="inlineStr"/>
-      <c r="E4" s="8" t="inlineStr"/>
-      <c r="F4" s="8" t="inlineStr"/>
-      <c r="G4" s="8" t="inlineStr"/>
-      <c r="H4" s="8" t="inlineStr"/>
+      <c r="E4" s="13" t="inlineStr">
+        <is>
+          <t>CS401
+LEC
+Room: 101
+Dr. C</t>
+        </is>
+      </c>
+      <c r="F4" s="10" t="n"/>
+      <c r="G4" s="10" t="n"/>
+      <c r="H4" s="11" t="n"/>
       <c r="I4" s="8" t="inlineStr"/>
       <c r="J4" s="8" t="inlineStr"/>
       <c r="K4" s="8" t="inlineStr"/>
@@ -2413,10 +2421,17 @@
       <c r="D5" s="8" t="inlineStr"/>
       <c r="E5" s="8" t="inlineStr"/>
       <c r="F5" s="8" t="inlineStr"/>
-      <c r="G5" s="8" t="inlineStr"/>
-      <c r="H5" s="8" t="inlineStr"/>
-      <c r="I5" s="8" t="inlineStr"/>
-      <c r="J5" s="8" t="inlineStr"/>
+      <c r="G5" s="13" t="inlineStr">
+        <is>
+          <t>CS401
+LEC
+Room: 101
+Dr. C</t>
+        </is>
+      </c>
+      <c r="H5" s="10" t="n"/>
+      <c r="I5" s="10" t="n"/>
+      <c r="J5" s="11" t="n"/>
       <c r="K5" s="8" t="inlineStr"/>
       <c r="L5" s="12" t="inlineStr">
         <is>
@@ -2448,14 +2463,7 @@
           <t>Minor Slot</t>
         </is>
       </c>
-      <c r="C6" s="9" t="inlineStr">
-        <is>
-          <t>CS401
-TUT
-Room: 101
-Dr. C</t>
-        </is>
-      </c>
+      <c r="C6" s="8" t="inlineStr"/>
       <c r="D6" s="8" t="inlineStr"/>
       <c r="E6" s="8" t="inlineStr"/>
       <c r="F6" s="8" t="inlineStr"/>
@@ -2469,15 +2477,8 @@
           <t>LUNCH BREAK</t>
         </is>
       </c>
-      <c r="M6" s="13" t="inlineStr">
-        <is>
-          <t>CS402
-LEC
-Room: 101
-Dr. D</t>
-        </is>
-      </c>
-      <c r="N6" s="11" t="n"/>
+      <c r="M6" s="8" t="inlineStr"/>
+      <c r="N6" s="8" t="inlineStr"/>
       <c r="O6" s="8" t="inlineStr"/>
       <c r="P6" s="8" t="inlineStr"/>
       <c r="Q6" s="8" t="inlineStr"/>
@@ -2586,11 +2587,12 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="M6:N6"/>
-    <mergeCell ref="P2:R2"/>
-    <mergeCell ref="M2:N2"/>
+  <mergeCells count="5">
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="E4:H4"/>
+    <mergeCell ref="O2:Q2"/>
     <mergeCell ref="M3:N3"/>
+    <mergeCell ref="G5:J5"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2602,7 +2604,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H17"/>
+  <dimension ref="A1:H19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2657,14 +2659,14 @@
         <v>2</v>
       </c>
       <c r="C2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D2" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Dr. A</t>
+          <t>Dr. B</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -2679,7 +2681,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>CS201</t>
+          <t>CS202</t>
         </is>
       </c>
     </row>
@@ -2693,10 +2695,10 @@
         <v>3</v>
       </c>
       <c r="C3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -2729,10 +2731,10 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D4" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -2765,14 +2767,14 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="D5" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Dr. B</t>
+          <t>Dr. A</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -2787,7 +2789,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>CS202</t>
+          <t>CS201</t>
         </is>
       </c>
     </row>
@@ -2801,14 +2803,14 @@
         <v>2</v>
       </c>
       <c r="C6" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D6" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Dr. A</t>
+          <t>Dr. B</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -2823,7 +2825,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>CS201</t>
+          <t>CS202</t>
         </is>
       </c>
     </row>
@@ -2837,10 +2839,10 @@
         <v>3</v>
       </c>
       <c r="C7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D7" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -2873,10 +2875,10 @@
         <v>3</v>
       </c>
       <c r="C8" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D8" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -2909,14 +2911,14 @@
         <v>4</v>
       </c>
       <c r="C9" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="D9" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Dr. B</t>
+          <t>Dr. A</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -2931,7 +2933,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>CS202</t>
+          <t>CS201</t>
         </is>
       </c>
     </row>
@@ -2945,10 +2947,10 @@
         <v>2</v>
       </c>
       <c r="C10" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="D10" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -2981,10 +2983,10 @@
         <v>2</v>
       </c>
       <c r="C11" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D11" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -2998,7 +3000,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>LEC</t>
+          <t>TUT</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -3024,7 +3026,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Dr. C</t>
+          <t>Dr. D</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -3039,7 +3041,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>CS401</t>
+          <t>CS402</t>
         </is>
       </c>
     </row>
@@ -3050,17 +3052,17 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C13" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="D13" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Dr. D</t>
+          <t>Dr. C</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -3075,28 +3077,28 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>CS402</t>
+          <t>CS401</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>CSE_4_B</t>
+          <t>CSE_4_A</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="D14" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Dr. D</t>
+          <t>Dr. C</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -3111,7 +3113,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>CS402</t>
+          <t>CS401</t>
         </is>
       </c>
     </row>
@@ -3125,14 +3127,14 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="D15" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Dr. C</t>
+          <t>Dr. D</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -3147,7 +3149,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>CS401</t>
+          <t>CS402</t>
         </is>
       </c>
     </row>
@@ -3158,13 +3160,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C16" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D16" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -3178,7 +3180,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>LEC</t>
+          <t>TUT</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -3194,7 +3196,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
         <v>13</v>
@@ -3220,6 +3222,78 @@
       <c r="H17" t="inlineStr">
         <is>
           <t>CS402</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>CSE_4_B</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>4</v>
+      </c>
+      <c r="C18" t="n">
+        <v>5</v>
+      </c>
+      <c r="D18" t="n">
+        <v>8</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Dr. C</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>LEC</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>CS401</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>CSE_4_B</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>5</v>
+      </c>
+      <c r="C19" t="n">
+        <v>7</v>
+      </c>
+      <c r="D19" t="n">
+        <v>10</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Dr. C</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>LEC</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>CS401</t>
         </is>
       </c>
     </row>
